--- a/static/standards-correlations/North_Dakota_CS1_State_Standards.xlsx
+++ b/static/standards-correlations/North_Dakota_CS1_State_Standards.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Crosswalk" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Legend &amp; Attribution" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Crosswalk'!$A$4:$I$33</definedName>
@@ -565,10 +565,11 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Scored against full lab bodies | C and Python tracks | Discovery Projects | May 2025 standards, implementation 2026-27 - the 2019 set is superseded</t>
-        </is>
-      </c>
-    </row>
+          <t>Scored against full lab bodies | C and Python tracks | Introductory Projects | May 2025 standards, implementation 2026-27 - the 2019 set is superseded</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
     <row r="4" ht="32" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -602,7 +603,7 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Discovery Projects</t>
+          <t>Introductory Projects</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
@@ -843,7 +844,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>One of the strongest matches in this file, and the hardware half is what makes it. Unit 1.1 carries a structured debugging process as a stated objective, and 64 prompts across the tracks require describing a bug by symptom, cause, and fix. Discovery Coding 3 asks what TWO things to check first when a program runs and nothing moves - which forces the software-against-hardware distinction directly, because on a real robot the answer may be an unplugged motor or the wrong port. Units 1.3, 1.4, 1.5, and 2.3 each carry a common-bugs callout naming that construct's characteristic failures, and a 100-term glossary supplies the specific terminology North Dakota asks for.</t>
+          <t>One of the strongest matches in this file, and the hardware half is what makes it. Unit 1.1 carries a structured debugging process as a stated objective, and 64 prompts across the tracks require describing a bug by symptom, cause, and fix. Introductory Coding 3 asks what TWO things to check first when a program runs and nothing moves - which forces the software-against-hardware distinction directly, because on a real robot the answer may be an unplugged motor or the wrong port. Units 1.3, 1.4, 1.5, and 2.3 each carry a common-bugs callout naming that construct's characteristic failures, and a 100-term glossary supplies the specific terminology North Dakota asks for.</t>
         </is>
       </c>
     </row>
@@ -980,7 +981,7 @@
       </c>
       <c r="I12" s="8" t="inlineStr">
         <is>
-          <t>All three verbs are met. RECOGNIZE: Unit 1.1 defines algorithm as a stated objective and Discovery Systems 4 has students recognise an algorithm in a drawn plan. DESIGN: Unit 3.5 plans a full multi-step mission before writing any code. USE: Unit 5.4 implements a sort and a linear search over real measurement data. ACROSS DISCIPLINES is served by Ext 4.1E (The Same Idea, Somewhere Else), which asks where else the measure-once-then-model pattern applies outside robotics.</t>
+          <t>All three verbs are met. RECOGNIZE: Unit 1.1 defines algorithm as a stated objective and Introductory Systems 4 has students recognise an algorithm in a drawn plan. DESIGN: Unit 3.5 plans a full multi-step mission before writing any code. USE: Unit 5.4 implements a sort and a linear search over real measurement data. ACROSS DISCIPLINES is served by Ext 4.1E (The Same Idea, Somewhere Else), which asks where else the measure-once-then-model pattern applies outside robotics.</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1169,7 @@
       </c>
       <c r="I16" s="8" t="inlineStr">
         <is>
-          <t>Unit 2.2 is this standard almost exactly, in core: students implement the SAME task two ways - braking and coasting - run five trials of each, discuss which is more consistent and why, and choose. The multiple-solutions-with-tradeoffs pattern repeats in Unit 5.2 (else-if chain against separate ifs) and Unit 5.4 (stored boolean against an inline check). Labs are team-based throughout and PreLab 0 establishes a shared working agreement; Discovery Systems 3 makes the cost of uncoordinated work explicit.</t>
+          <t>Unit 2.2 is this standard almost exactly, in core: students implement the SAME task two ways - braking and coasting - run five trials of each, discuss which is more consistent and why, and choose. The multiple-solutions-with-tradeoffs pattern repeats in Unit 5.2 (else-if chain against separate ifs) and Unit 5.4 (stored boolean against an inline check). Labs are team-based throughout and PreLab 0 establishes a shared working agreement; Introductory Systems 3 makes the cost of uncoordinated work explicit.</t>
         </is>
       </c>
     </row>
@@ -1387,7 +1388,7 @@
       </c>
       <c r="I21" s="8" t="inlineStr">
         <is>
-          <t>Three of North Dakota's four named issues have core evidence, and the responsibility clause is met unusually directly. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). - that is the responsibility of users and creators, asked repeatedly and in core. PRIVACY: Ext 2.6E (Automatic Data Collection) names continuous collection with nobody approving each individual reading. INTELLECTUAL PROPERTY: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. AI: the AI Literacy Bridge throughout. Discovery Systems 12 asks whose job it is to anticipate harm from something genuinely useful. Location sharing is the one named issue not covered.</t>
+          <t>Three of North Dakota's four named issues have core evidence, and the responsibility clause is met unusually directly. Nineteen reflection prompts address responsibility for automated-system errors (navigation misroute, spam misflag, freight misclassification). - that is the responsibility of users and creators, asked repeatedly and in core. PRIVACY: Ext 2.6E (Automatic Data Collection) names continuous collection with nobody approving each individual reading. INTELLECTUAL PROPERTY: Lab 5.3 core teaches the MIT License by name: what it permits and the single condition it imposes. AI: the AI Literacy Bridge throughout. Introductory Systems 12 asks whose job it is to anticipate harm from something genuinely useful. Location sharing is the one named issue not covered.</t>
         </is>
       </c>
     </row>
@@ -1555,7 +1556,7 @@
       <c r="H25" s="12" t="n"/>
       <c r="I25" s="11" t="inlineStr">
         <is>
-          <t>NOT ADDRESSED. Personal media usage, screen time, and media balance appear nowhere in either track or in the Discovery projects. The curriculum has no digital-wellness component. Same gap recorded against Virginia CSF.IC.2 and Florida SC.912.HS.2.</t>
+          <t>NOT ADDRESSED. Personal media usage, screen time, and media balance appear nowhere in either track or in the Introductory projects. The curriculum has no digital-wellness component. Same gap recorded against Virginia CSF.IC.2 and Florida SC.912.HS.2.</t>
         </is>
       </c>
     </row>
@@ -1905,6 +1906,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="14" t="inlineStr">
         <is>
@@ -1949,7 +1951,7 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Coding strand, project NN (01-17).</t>
+          <t>Introductory Project, Coding strand, project NN (01-17).</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1963,7 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Discovery Project, Systems strand, project NN (01-14).</t>
+          <t>Introductory Project, Systems strand, project NN (01-14).</t>
         </is>
       </c>
     </row>
@@ -2097,6 +2099,8 @@
         </is>
       </c>
     </row>
+    <row r="19"/>
+    <row r="20"/>
     <row r="21">
       <c r="A21" s="13" t="inlineStr">
         <is>
@@ -2124,7 +2128,7 @@
 MANDATE CONTEXT: computer science courses can count as a MATHEMATICS credit toward graduation in North Dakota. Statutory basis NDCC 15.1-21-01(2) and 15.1-21-02(2)(b). That is the practical route into a North Dakota master schedule, and the mathematical content of Unit 4 (a ticks_per_inch model built from measurement) and Unit 5 (y = mx + b speed ramp, integer division and modulo) supports the claim.
 Crosswalk analysis (c) KIPR / Botball Explorer.
 === METHODOLOGY (revised) ===
-Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Discovery projects.
+Scored against FULL LAB BODIES: reflection prompts, Individual Reflection phases, AI Literacy Bridge sections, and Extension Challenges. Evidence base is 750 reflection prompts and 255 Extension Challenges across 27 C labs, 27 Python labs, and 31 Introductory projects.
 Scoring rule: Full requires evidence in the core lab flow. Partial is assigned where the only evidence sits in an optional Extension Challenge (labelled 'Finished early?'), or where the standard is only partly met.
 RESULT: 9 Full, 15 Partial, 5 blank of 29. Read BY CONCEPT.
   Algorithms and Computational Thinking  6 Full, 0 Partial, 1 blank of 7   - very strong
